--- a/data/trans_dic/IP18A01-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP18A01-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación</t>
+          <t>Menores que su última consulta al médico fue por vacunación (tasa de respuesta: 98,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,52</t>
+          <t>1,65; 7,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,78; 16,23</t>
+          <t>6,83; 16,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 15,51</t>
+          <t>6,17; 15,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,89</t>
+          <t>0,0; 28,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 7,96</t>
+          <t>2,05; 8,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 14,79</t>
+          <t>6,4; 15,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,43; 14,19</t>
+          <t>5,52; 13,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,03</t>
+          <t>2,61; 6,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 13,53</t>
+          <t>7,37; 13,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,58; 12,73</t>
+          <t>6,78; 13,03</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,24</t>
+          <t>0,0; 14,16</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,11; 10,25</t>
+          <t>4,44; 10,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 10,38</t>
+          <t>4,63; 11,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 10,91</t>
+          <t>4,98; 10,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 18,38</t>
+          <t>2,71; 19,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 9,4</t>
+          <t>3,55; 9,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,92; 12,65</t>
+          <t>5,72; 12,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,18; 12,62</t>
+          <t>5,77; 12,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 14,83</t>
+          <t>3,18; 15,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,41; 8,42</t>
+          <t>4,4; 8,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,78; 10,38</t>
+          <t>5,92; 10,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,25; 10,45</t>
+          <t>6,19; 10,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 13,26</t>
+          <t>4,0; 12,95</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,33; 15,5</t>
+          <t>7,25; 15,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 12,76</t>
+          <t>5,51; 13,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,56; 13,41</t>
+          <t>5,48; 13,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,73</t>
+          <t>0,0; 16,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 14,45</t>
+          <t>6,22; 14,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 13,66</t>
+          <t>5,96; 13,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,83; 12,62</t>
+          <t>5,06; 13,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,29</t>
+          <t>0,0; 5,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,61; 13,39</t>
+          <t>7,68; 13,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,44; 11,9</t>
+          <t>6,31; 11,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,01; 11,88</t>
+          <t>6,01; 11,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 8,12</t>
+          <t>0,67; 7,72</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,89; 15,95</t>
+          <t>7,94; 15,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,01; 17,18</t>
+          <t>9,25; 17,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,45; 15,32</t>
+          <t>7,82; 15,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 19,83</t>
+          <t>0,0; 21,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,61; 16,62</t>
+          <t>8,91; 16,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,57; 15,84</t>
+          <t>8,21; 15,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,8; 13,0</t>
+          <t>5,88; 13,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,48</t>
+          <t>0,0; 14,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,48; 14,82</t>
+          <t>9,19; 14,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,81; 15,68</t>
+          <t>9,74; 15,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,49; 13,4</t>
+          <t>7,41; 12,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 12,81</t>
+          <t>2,28; 13,36</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,81; 10,52</t>
+          <t>6,86; 10,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,98; 11,86</t>
+          <t>7,97; 11,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,76; 11,4</t>
+          <t>7,51; 11,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 12,66</t>
+          <t>3,62; 12,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,59; 10,17</t>
+          <t>6,64; 10,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,26; 12,31</t>
+          <t>8,19; 11,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,86; 10,76</t>
+          <t>7,07; 10,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 7,47</t>
+          <t>1,93; 7,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,2; 9,94</t>
+          <t>7,18; 9,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,61; 11,22</t>
+          <t>8,65; 11,42</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,91; 10,46</t>
+          <t>7,84; 10,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,11</t>
+          <t>3,53; 8,14</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su última consulta al médico fue por vacunación (tasa de respuesta: 98,73%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4624</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13541</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5931</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>14804</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>12462</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>10554</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>28345</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>24763</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1902; 8771</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8822; 20844</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7574; 19281</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4874</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2639; 11389</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>9349; 22909</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7468; 18467</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>6387; 16601</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>20275; 36862</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>17497; 33627</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5483</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>11223</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13300</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14531</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2341</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>10389</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>18306</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3761</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>21612</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>31408</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>32837</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>6102</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>7344; 17286</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>8819; 21063</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>9628; 20876</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>784; 5575</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>6385; 16193</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>11710; 26424</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>12045; 25153</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1581; 7606</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>15189; 29917</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>23389; 40754</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>24873; 43134</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3148; 10195</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>13350</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12337</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12392</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1231</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>13261</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>14042</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>11752</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>26611</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>26378</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>24144</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1627</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>9036; 19279</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7830; 18888</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7456; 18519</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4260</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8321; 19094</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>9276; 21501</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7244; 18956</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 1867</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>19854; 34302</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>18778; 34384</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>16777; 32482</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>390; 4468</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>21930</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25931</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21024</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2305</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>22605</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1186</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>44535</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>49797</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>37125</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>15297; 29831</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>18708; 35596</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>14718; 29362</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5948</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>16149; 30223</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>16527; 31856</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>10730; 23830</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4183</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>34365; 55677</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>39310; 61433</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>27474; 47695</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1287; 7559</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>51127</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>65108</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>60248</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>52186</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>70819</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>58621</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5343</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>103313</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>135927</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>118869</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>12503</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>41000; 62606</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>52879; 77802</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>48061; 73365</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>3635; 12644</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>41419; 64291</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>57925; 84753</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>47364; 70654</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2536; 9440</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>87795; 118659</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>118617; 156587</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>102744; 138204</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>8178; 18872</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP18A01-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP18A01-Habitat-trans_dic.xlsx
@@ -717,37 +717,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,59</t>
+          <t>1,68; 7,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 16,15</t>
+          <t>6,19; 15,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,17; 15,7</t>
+          <t>5,69; 15,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,58</t>
+          <t>0,0; 26,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 8,83</t>
+          <t>2,46; 8,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,4; 15,68</t>
+          <t>6,28; 15,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,52; 13,64</t>
+          <t>5,64; 14,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,79</t>
+          <t>2,45; 6,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,37; 13,39</t>
+          <t>7,55; 13,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,78; 13,03</t>
+          <t>6,82; 13,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,16</t>
+          <t>0,0; 14,4</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,44; 10,45</t>
+          <t>4,19; 10,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,63; 11,06</t>
+          <t>4,36; 10,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 10,8</t>
+          <t>4,73; 10,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 19,24</t>
+          <t>2,67; 19,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,55; 9,0</t>
+          <t>3,33; 8,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 12,91</t>
+          <t>5,91; 12,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 12,05</t>
+          <t>6,17; 12,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 15,29</t>
+          <t>3,24; 14,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,4; 8,66</t>
+          <t>4,37; 8,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,92; 10,32</t>
+          <t>5,91; 10,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 10,73</t>
+          <t>6,21; 10,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 12,95</t>
+          <t>4,09; 13,43</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 15,48</t>
+          <t>6,96; 15,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,51; 13,3</t>
+          <t>5,58; 12,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,48; 13,62</t>
+          <t>5,84; 14,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,24</t>
+          <t>0,0; 16,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,22; 14,27</t>
+          <t>6,4; 14,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,96; 13,82</t>
+          <t>5,75; 13,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 13,23</t>
+          <t>4,62; 12,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,89</t>
+          <t>0,0; 7,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,68; 13,28</t>
+          <t>7,69; 13,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,31; 11,55</t>
+          <t>6,74; 11,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,01; 11,63</t>
+          <t>6,08; 11,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 7,72</t>
+          <t>0,65; 8,31</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,94; 15,49</t>
+          <t>7,86; 15,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,25; 17,6</t>
+          <t>9,17; 17,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,82; 15,6</t>
+          <t>7,48; 15,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,21</t>
+          <t>2,65; 21,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,91; 16,67</t>
+          <t>8,6; 16,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,21; 15,82</t>
+          <t>8,39; 15,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,88; 13,07</t>
+          <t>5,89; 12,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,67</t>
+          <t>0,0; 12,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,19; 14,89</t>
+          <t>9,34; 14,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,74; 15,22</t>
+          <t>9,63; 15,49</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,41; 12,87</t>
+          <t>7,54; 12,58</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 13,36</t>
+          <t>2,36; 13,28</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,86; 10,47</t>
+          <t>7,05; 10,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,97; 11,72</t>
+          <t>8,12; 11,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,51; 11,46</t>
+          <t>7,65; 11,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,62; 12,6</t>
+          <t>3,76; 12,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,64; 10,3</t>
+          <t>6,67; 10,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,19; 11,98</t>
+          <t>8,25; 12,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,07; 10,55</t>
+          <t>7,16; 10,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 7,17</t>
+          <t>1,92; 7,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,18; 9,71</t>
+          <t>7,27; 9,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,65; 11,42</t>
+          <t>8,68; 11,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,84; 10,55</t>
+          <t>7,84; 10,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 8,14</t>
+          <t>3,33; 8,02</t>
         </is>
       </c>
     </row>
@@ -1645,37 +1645,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1902; 8771</t>
+          <t>1941; 8910</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8822; 20844</t>
+          <t>7988; 19867</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7574; 19281</t>
+          <t>6990; 18788</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4874</t>
+          <t>0; 4602</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2639; 11389</t>
+          <t>3176; 10710</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9349; 22909</t>
+          <t>9181; 21963</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7468; 18467</t>
+          <t>7629; 19007</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6387; 16601</t>
+          <t>5997; 15890</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20275; 36862</t>
+          <t>20776; 38432</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17497; 33627</t>
+          <t>17616; 33983</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 5483</t>
+          <t>0; 5576</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7344; 17286</t>
+          <t>6929; 17343</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8819; 21063</t>
+          <t>8299; 19534</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9628; 20876</t>
+          <t>9142; 20330</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>784; 5575</t>
+          <t>773; 5784</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6385; 16193</t>
+          <t>5983; 15793</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11710; 26424</t>
+          <t>12091; 26087</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12045; 25153</t>
+          <t>12888; 26325</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1581; 7606</t>
+          <t>1611; 7357</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15189; 29917</t>
+          <t>15085; 28835</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23389; 40754</t>
+          <t>23358; 41197</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24873; 43134</t>
+          <t>24978; 41730</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3148; 10195</t>
+          <t>3223; 10568</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9036; 19279</t>
+          <t>8676; 19010</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7830; 18888</t>
+          <t>7930; 18422</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7456; 18519</t>
+          <t>7948; 19194</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4260</t>
+          <t>0; 4259</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8321; 19094</t>
+          <t>8557; 19335</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9276; 21501</t>
+          <t>8939; 21275</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7244; 18956</t>
+          <t>6619; 17873</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 1867</t>
+          <t>0; 2234</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19854; 34302</t>
+          <t>19868; 34879</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18778; 34384</t>
+          <t>20072; 34925</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16777; 32482</t>
+          <t>16982; 32225</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>390; 4468</t>
+          <t>376; 4814</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15297; 29831</t>
+          <t>15140; 29927</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18708; 35596</t>
+          <t>18549; 35401</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14718; 29362</t>
+          <t>14080; 29003</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5948</t>
+          <t>743; 6127</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16149; 30223</t>
+          <t>15598; 30615</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16527; 31856</t>
+          <t>16890; 31987</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10730; 23830</t>
+          <t>10735; 23266</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4183</t>
+          <t>0; 3592</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34365; 55677</t>
+          <t>34926; 55814</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39310; 61433</t>
+          <t>38874; 62497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27474; 47695</t>
+          <t>27951; 46624</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1287; 7559</t>
+          <t>1334; 7511</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>41000; 62606</t>
+          <t>42169; 63698</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>52879; 77802</t>
+          <t>53923; 77796</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48061; 73365</t>
+          <t>49014; 74082</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3635; 12644</t>
+          <t>3769; 12784</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>41419; 64291</t>
+          <t>41648; 64459</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57925; 84753</t>
+          <t>58366; 85503</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47364; 70654</t>
+          <t>47953; 72760</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2536; 9440</t>
+          <t>2529; 10005</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>87795; 118659</t>
+          <t>88837; 120141</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>118617; 156587</t>
+          <t>119009; 155819</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>102744; 138204</t>
+          <t>102758; 135141</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8178; 18872</t>
+          <t>7716; 18602</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP18A01-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP18A01-Habitat-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación (tasa de respuesta: 98,73%)</t>
+          <t>Menores cuya última consulta médica fue por vacunación (tasa de respuesta: 98,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10,13%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>10,49%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>10,02%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,52%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,13%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 7,71</t>
+          <t>2,45; 7,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,19; 15,39</t>
+          <t>6,16; 14,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 15,3</t>
+          <t>5,43; 14,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 8,3</t>
+          <t>1,65; 7,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,28; 15,03</t>
+          <t>6,78; 16,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 14,04</t>
+          <t>6,31; 15,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 27,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 6,5</t>
+          <t>2,73; 7,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,55; 13,96</t>
+          <t>7,43; 13,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,82; 13,16</t>
+          <t>6,58; 12,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,4</t>
+          <t>0,0; 13,8</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,77%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8,77%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>6,79%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>6,99%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>7,52%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8,08%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,85%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 10,49</t>
+          <t>3,56; 9,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,36; 10,26</t>
+          <t>5,92; 12,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 10,52</t>
+          <t>6,18; 12,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,67; 19,96</t>
+          <t>2,67; 14,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 8,78</t>
+          <t>4,11; 10,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,91; 12,75</t>
+          <t>4,23; 10,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 12,61</t>
+          <t>4,83; 10,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 14,79</t>
+          <t>2,64; 19,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 8,35</t>
+          <t>4,41; 8,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,91; 10,43</t>
+          <t>5,78; 10,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,21; 10,38</t>
+          <t>6,25; 10,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 13,43</t>
+          <t>4,04; 13,49</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,91%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,02%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8,2%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>10,72%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>8,68%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>9,11%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,2%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,96; 15,26</t>
+          <t>6,56; 14,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,58; 12,97</t>
+          <t>5,62; 13,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,84; 14,11</t>
+          <t>4,83; 12,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,23</t>
+          <t>0,0; 5,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 14,45</t>
+          <t>7,33; 15,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,75; 13,67</t>
+          <t>5,62; 12,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 12,48</t>
+          <t>5,56; 13,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,05</t>
+          <t>0,0; 18,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,69; 13,5</t>
+          <t>7,61; 13,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,74; 11,73</t>
+          <t>6,44; 11,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,08; 11,54</t>
+          <t>6,01; 11,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 8,31</t>
+          <t>0,55; 7,67</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12,47%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>11,39%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>12,82%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>11,17%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,47%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,86%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,83%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 15,54</t>
+          <t>8,61; 16,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,17; 17,5</t>
+          <t>8,57; 15,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,48; 15,41</t>
+          <t>5,8; 13,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 21,84</t>
+          <t>0,0; 13,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,6; 16,89</t>
+          <t>7,89; 15,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,39; 15,89</t>
+          <t>9,01; 17,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,89; 12,76</t>
+          <t>7,45; 15,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,6</t>
+          <t>2,6; 20,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,34; 14,93</t>
+          <t>9,48; 14,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,63; 15,49</t>
+          <t>9,81; 15,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 12,58</t>
+          <t>7,49; 13,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 13,28</t>
+          <t>2,24; 13,18</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8,75%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>8,55%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>9,81%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>9,41%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,36%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,05; 10,65</t>
+          <t>6,59; 10,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,12; 11,72</t>
+          <t>8,26; 12,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,65; 11,57</t>
+          <t>6,86; 10,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 12,74</t>
+          <t>1,87; 7,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,67; 10,33</t>
+          <t>6,81; 10,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,25; 12,08</t>
+          <t>7,98; 11,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,16; 10,86</t>
+          <t>7,76; 11,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,6</t>
+          <t>3,45; 12,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,27; 9,83</t>
+          <t>7,2; 9,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,68; 11,36</t>
+          <t>8,61; 11,22</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,84; 10,32</t>
+          <t>7,91; 10,46</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 8,02</t>
+          <t>3,35; 8,23</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación (tasa de respuesta: 98,73%)</t>
+          <t>Menores cuya última consulta médica fue por vacunación (tasa de respuesta: 98,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5931</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14804</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12462</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>4624</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>13541</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>12301</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1283</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5931</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>14804</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>12462</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1941; 8910</t>
+          <t>3161; 10273</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7988; 19867</t>
+          <t>9004; 21619</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6990; 18788</t>
+          <t>7343; 19209</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4602</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3176; 10710</t>
+          <t>1908; 8685</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9181; 21963</t>
+          <t>8754; 20947</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7629; 19007</t>
+          <t>7750; 19049</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4795</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5997; 15890</t>
+          <t>6672; 17197</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20776; 38432</t>
+          <t>20461; 37229</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17616; 33983</t>
+          <t>16996; 32857</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 5576</t>
+          <t>0; 5131</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10389</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18107</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18306</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3273</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>11223</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>13300</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>14531</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2341</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10389</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18107</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18306</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3761</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>5454</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6929; 17343</t>
+          <t>6400; 16912</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8299; 19534</t>
+          <t>12120; 25890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9142; 20330</t>
+          <t>12900; 26345</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>773; 5784</t>
+          <t>1214; 6801</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5983; 15793</t>
+          <t>6804; 16957</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12091; 26087</t>
+          <t>8060; 19751</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12888; 26325</t>
+          <t>9334; 21092</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1611; 7357</t>
+          <t>711; 5386</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15085; 28835</t>
+          <t>15223; 29060</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23358; 41197</t>
+          <t>22842; 41013</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24978; 41730</t>
+          <t>25127; 42016</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3223; 10568</t>
+          <t>2924; 9756</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>13261</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14042</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>11752</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>13350</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>12337</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>12392</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1231</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>13261</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>14042</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>11752</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>1347</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8676; 19010</t>
+          <t>8783; 19334</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7930; 18422</t>
+          <t>8738; 21255</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7948; 19194</t>
+          <t>6916; 18088</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4259</t>
+          <t>0; 1571</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8557; 19335</t>
+          <t>9130; 19310</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8939; 21275</t>
+          <t>7984; 18125</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6619; 17873</t>
+          <t>7556; 18244</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2234</t>
+          <t>0; 4345</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19868; 34879</t>
+          <t>19672; 34584</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20072; 34925</t>
+          <t>19176; 35409</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16982; 32225</t>
+          <t>16796; 33177</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>376; 4814</t>
+          <t>298; 4133</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>22605</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>21930</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>25931</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>21024</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2305</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>22605</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>16101</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3303</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15140; 29927</t>
+          <t>15605; 30127</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18549; 35401</t>
+          <t>17249; 31888</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14080; 29003</t>
+          <t>10577; 23696</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>743; 6127</t>
+          <t>0; 3467</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15598; 30615</t>
+          <t>15188; 30701</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16890; 31987</t>
+          <t>18217; 34744</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10735; 23266</t>
+          <t>14015; 28837</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3592</t>
+          <t>720; 5609</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34926; 55814</t>
+          <t>35447; 55406</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38874; 62497</t>
+          <t>39601; 63271</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27951; 46624</t>
+          <t>27745; 49638</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1334; 7511</t>
+          <t>1205; 7092</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>52186</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>70819</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>58621</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4549</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>51127</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>65108</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>60248</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>7160</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>52186</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>70819</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>58621</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>11387</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>42169; 63698</t>
+          <t>41097; 63437</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>53923; 77796</t>
+          <t>58462; 87104</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49014; 74082</t>
+          <t>45971; 72075</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3769; 12784</t>
+          <t>2282; 8806</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>41648; 64459</t>
+          <t>40701; 62933</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58366; 85503</t>
+          <t>52968; 78747</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47953; 72760</t>
+          <t>49663; 72997</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2529; 10005</t>
+          <t>3298; 12315</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>88837; 120141</t>
+          <t>87981; 121498</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>119009; 155819</t>
+          <t>118088; 153873</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>102758; 135141</t>
+          <t>103583; 137035</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7716; 18602</t>
+          <t>7286; 17885</t>
         </is>
       </c>
     </row>
